--- a/Data/PlayerLevel.xlsx
+++ b/Data/PlayerLevel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\files (10)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F0B794-211C-4637-94BF-2F10306918D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F4352E-4F2C-458F-A53C-6F1D1BB92296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5955" yWindow="1335" windowWidth="30045" windowHeight="16455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerLevel" sheetId="1" r:id="rId1"/>
@@ -34,97 +34,97 @@
     <t>BaseStats</t>
   </si>
   <si>
-    <t>Attack=2|HP=10|Defence=1</t>
-  </si>
-  <si>
-    <t>Attack=2|HP=15|Defence=1</t>
-  </si>
-  <si>
-    <t>Attack=3|HP=20|Defence=1</t>
-  </si>
-  <si>
-    <t>Attack=3|HP=25|Defence=1</t>
-  </si>
-  <si>
-    <t>Attack=4|HP=30|Defence=2</t>
-  </si>
-  <si>
-    <t>Attack=4|HP=35|Defence=2</t>
-  </si>
-  <si>
-    <t>Attack=5|HP=40|Defence=2</t>
-  </si>
-  <si>
-    <t>Attack=5|HP=45|Defence=2</t>
-  </si>
-  <si>
-    <t>Attack=6|HP=50|Defence=3</t>
-  </si>
-  <si>
-    <t>Attack=6|HP=55|Defence=3</t>
-  </si>
-  <si>
-    <t>Attack=7|HP=60|Defence=3</t>
-  </si>
-  <si>
-    <t>Attack=7|HP=65|Defence=3</t>
-  </si>
-  <si>
-    <t>Attack=8|HP=70|Defence=4</t>
-  </si>
-  <si>
-    <t>Attack=8|HP=75|Defence=4</t>
-  </si>
-  <si>
-    <t>Attack=9|HP=80|Defence=4</t>
-  </si>
-  <si>
-    <t>Attack=9|HP=85|Defence=4</t>
-  </si>
-  <si>
-    <t>Attack=10|HP=90|Defence=5</t>
-  </si>
-  <si>
-    <t>Attack=10|HP=95|Defence=5</t>
-  </si>
-  <si>
-    <t>Attack=11|HP=100|Defence=5</t>
-  </si>
-  <si>
-    <t>Attack=11|HP=105|Defence=5</t>
-  </si>
-  <si>
-    <t>Attack=12|HP=110|Defence=6</t>
-  </si>
-  <si>
-    <t>Attack=12|HP=115|Defence=6</t>
-  </si>
-  <si>
-    <t>Attack=13|HP=120|Defence=6</t>
-  </si>
-  <si>
-    <t>Attack=13|HP=125|Defence=6</t>
-  </si>
-  <si>
-    <t>Attack=14|HP=130|Defence=7</t>
-  </si>
-  <si>
-    <t>Attack=14|HP=135|Defence=7</t>
-  </si>
-  <si>
-    <t>Attack=15|HP=140|Defence=7</t>
-  </si>
-  <si>
-    <t>Attack=15|HP=145|Defence=7</t>
-  </si>
-  <si>
-    <t>Attack=16|HP=150|Defence=8</t>
-  </si>
-  <si>
-    <t>Attack=16|HP=155|Defence=8</t>
-  </si>
-  <si>
-    <t>Attack=17|HP=160|Defence=8</t>
+    <t>Attack=2;HP=10;Defence=1</t>
+  </si>
+  <si>
+    <t>Attack=2;HP=15;Defence=1</t>
+  </si>
+  <si>
+    <t>Attack=3;HP=20;Defence=1</t>
+  </si>
+  <si>
+    <t>Attack=3;HP=25;Defence=1</t>
+  </si>
+  <si>
+    <t>Attack=4;HP=30;Defence=2</t>
+  </si>
+  <si>
+    <t>Attack=4;HP=35;Defence=2</t>
+  </si>
+  <si>
+    <t>Attack=5;HP=40;Defence=2</t>
+  </si>
+  <si>
+    <t>Attack=5;HP=45;Defence=2</t>
+  </si>
+  <si>
+    <t>Attack=6;HP=50;Defence=3</t>
+  </si>
+  <si>
+    <t>Attack=6;HP=55;Defence=3</t>
+  </si>
+  <si>
+    <t>Attack=7;HP=60;Defence=3</t>
+  </si>
+  <si>
+    <t>Attack=7;HP=65;Defence=3</t>
+  </si>
+  <si>
+    <t>Attack=8;HP=70;Defence=4</t>
+  </si>
+  <si>
+    <t>Attack=8;HP=75;Defence=4</t>
+  </si>
+  <si>
+    <t>Attack=9;HP=80;Defence=4</t>
+  </si>
+  <si>
+    <t>Attack=9;HP=85;Defence=4</t>
+  </si>
+  <si>
+    <t>Attack=10;HP=90;Defence=5</t>
+  </si>
+  <si>
+    <t>Attack=10;HP=95;Defence=5</t>
+  </si>
+  <si>
+    <t>Attack=11;HP=100;Defence=5</t>
+  </si>
+  <si>
+    <t>Attack=11;HP=105;Defence=5</t>
+  </si>
+  <si>
+    <t>Attack=12;HP=110;Defence=6</t>
+  </si>
+  <si>
+    <t>Attack=12;HP=115;Defence=6</t>
+  </si>
+  <si>
+    <t>Attack=13;HP=120;Defence=6</t>
+  </si>
+  <si>
+    <t>Attack=13;HP=125;Defence=6</t>
+  </si>
+  <si>
+    <t>Attack=14;HP=130;Defence=7</t>
+  </si>
+  <si>
+    <t>Attack=14;HP=135;Defence=7</t>
+  </si>
+  <si>
+    <t>Attack=15;HP=140;Defence=7</t>
+  </si>
+  <si>
+    <t>Attack=15;HP=145;Defence=7</t>
+  </si>
+  <si>
+    <t>Attack=16;HP=150;Defence=8</t>
+  </si>
+  <si>
+    <t>Attack=16;HP=155;Defence=8</t>
+  </si>
+  <si>
+    <t>Attack=17;HP=160;Defence=8</t>
   </si>
 </sst>
 </file>
